--- a/Unity/GameData/DataTables/LevelTable.xlsx
+++ b/Unity/GameData/DataTables/LevelTable.xlsx
@@ -1320,10 +1320,10 @@
         <v>13</v>
       </c>
       <c r="E5">
-        <v>51</v>
+        <v>17</v>
       </c>
       <c r="F5">
-        <v>64</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" spans="2:6">
@@ -1337,10 +1337,10 @@
         <v>15</v>
       </c>
       <c r="E6">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="F6">
-        <v>50</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7" spans="2:6">
@@ -1354,10 +1354,10 @@
         <v>17</v>
       </c>
       <c r="E7">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="F7">
-        <v>35</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8" spans="2:6">
@@ -1371,10 +1371,10 @@
         <v>19</v>
       </c>
       <c r="E8">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="F8">
-        <v>25</v>
+        <v>64</v>
       </c>
     </row>
   </sheetData>
